--- a/training_forms/027_rapid_sequence_intubation_quiz--training_forms.xlsx
+++ b/training_forms/027_rapid_sequence_intubation_quiz--training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3511,12 +3511,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
